--- a/dataset_t6_grouped/results2/G3/G3_T7503_W0058F0002T0006Z000C1N55_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G3/G3_T7503_W0058F0002T0006Z000C1N55_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>58.38534697888255</v>
+        <v>9.487618884068414</v>
       </c>
       <c r="D2" t="n">
-        <v>58.67944197244148</v>
+        <v>9.53540932052174</v>
       </c>
       <c r="E2" t="n">
-        <v>13.62271638941752</v>
+        <v>2.213691413280346</v>
       </c>
       <c r="F2" t="n">
-        <v>13.41979664277666</v>
+        <v>2.180716954451207</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>42.67635129240999</v>
+        <v>6.934907085016624</v>
       </c>
       <c r="D3" t="n">
-        <v>42.45493611820371</v>
+        <v>6.898927119208103</v>
       </c>
       <c r="E3" t="n">
-        <v>13.62271638941752</v>
+        <v>2.213691413280346</v>
       </c>
       <c r="F3" t="n">
-        <v>13.41979664277666</v>
+        <v>2.180716954451207</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>71.04180743998877</v>
+        <v>11.54429370899818</v>
       </c>
       <c r="D4" t="n">
-        <v>70.45513401819672</v>
+        <v>11.44895927795697</v>
       </c>
       <c r="E4" t="n">
-        <v>13.62271638941752</v>
+        <v>2.213691413280346</v>
       </c>
       <c r="F4" t="n">
-        <v>13.41979664277666</v>
+        <v>2.180716954451207</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>78.61122043057283</v>
+        <v>12.77432331996808</v>
       </c>
       <c r="D5" t="n">
-        <v>78.01507168251973</v>
+        <v>12.67744914840946</v>
       </c>
       <c r="E5" t="n">
-        <v>13.62271638941752</v>
+        <v>2.213691413280346</v>
       </c>
       <c r="F5" t="n">
-        <v>13.41979664277666</v>
+        <v>2.180716954451207</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
